--- a/Data/Bioerosion_Data_TEMPLATE.xlsx
+++ b/Data/Bioerosion_Data_TEMPLATE.xlsx
@@ -697,15 +697,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca57789ecb406bb7a99068f68ac4c0ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89dc4794f4784a0bac47690674a3da53" ns2:_="" ns3:_="">
     <xsd:import namespace="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
@@ -900,6 +891,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -912,14 +912,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A206479D-07AC-477F-8545-4966E63B8E30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A81EFD0C-A7A2-40CC-AF34-FA5F0D62D046}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -938,6 +930,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A206479D-07AC-477F-8545-4966E63B8E30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FB6342C-EC7C-49F8-97E7-6339AB75B937}">
   <ds:schemaRefs>

--- a/Data/Bioerosion_Data_TEMPLATE.xlsx
+++ b/Data/Bioerosion_Data_TEMPLATE.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp.sharepoint.com/sites/usgs-carbonate_budget_restoration_tool/Shared Documents/Carbonate Budget Tool Collaboration/Carbonate_Budget_Tool_Code/CarbonateBudgetRestorationTool/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{BCECB760-554F-480D-81A5-8796C1F3ECE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{011036E6-85BD-4685-920E-4AEB83B9AD80}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{BCECB760-554F-480D-81A5-8796C1F3ECE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9191DF20-BC3A-43B6-AA2F-EFA9F8A85594}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{19050643-5FB9-4299-B24C-C8F9EBB4329D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{19050643-5FB9-4299-B24C-C8F9EBB4329D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Parrotfish" sheetId="1" r:id="rId1"/>
-    <sheet name="Urchins" sheetId="2" r:id="rId2"/>
-    <sheet name="Sponges" sheetId="3" r:id="rId3"/>
+    <sheet name="README" sheetId="4" r:id="rId1"/>
+    <sheet name="Parrotfish" sheetId="1" r:id="rId2"/>
+    <sheet name="Urchins" sheetId="2" r:id="rId3"/>
+    <sheet name="Sponges" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -75,87 +76,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Toth, Lauren T</author>
-    <author>tc={E0961E5A-6428-4F0A-89BB-DD3400C64C05}</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{EFCDC556-E34D-46BC-BEEE-08C4248F0336}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Toth, Lauren T:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-This will be displayed on the map
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="1" shapeId="0" xr:uid="{E0961E5A-6428-4F0A-89BB-DD3400C64C05}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    If blank will default to regional average</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Toth, Lauren T</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{BDA8E37F-BFB1-4FC1-8626-265B749DAF04}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Toth, Lauren T:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-This will be displayed on the map
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>Taxon</t>
   </si>
@@ -169,9 +91,6 @@
     <t>Unique_Site_ID</t>
   </si>
   <si>
-    <t>Survey_Area_m2</t>
-  </si>
-  <si>
     <t>Fork_length_cm</t>
   </si>
   <si>
@@ -179,13 +98,82 @@
   </si>
   <si>
     <t>Test_Diameter_mm</t>
+  </si>
+  <si>
+    <t>Bioerosion Data Input README:</t>
+  </si>
+  <si>
+    <t>• Within each tab, all fields are required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• It is not required that users input data in all tabs </t>
+  </si>
+  <si>
+    <t>• For example, users could enter parrotfish data without entering data on urchins or sponges; this will allow site-specific bioerosion to be calculated, while subregional- and habitat-specific averages will be used for urchins and sponges</t>
+  </si>
+  <si>
+    <t>Parrotfish</t>
+  </si>
+  <si>
+    <t>• The Unique_Site_ID for this data input must match the Unique_Site_ID in the Restoration_Monitoring_Cover_TEMPLATE</t>
+  </si>
+  <si>
+    <t>• Allowable fields for Taxon include: Sparisoma viride, Sparisoma aurofrenatum, Sparisoma rubripinne, Sparisoma chrysopterum, Scarus vetula, Scarus taeniopterus, Scarus iseri, Scarus guacamaia, Scarus coelestinus, Scarus coeruleus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Users must indicate the life phase of each observed parrotfish (initial phase or terminal phase). </t>
+  </si>
+  <si>
+    <t>•  Count is the number of parrotfish of each species, size class, and life phase observed within the survey area</t>
+  </si>
+  <si>
+    <t>Urchins</t>
+  </si>
+  <si>
+    <t>• Allowable fields for Taxon include: Diadema antillarum, Echinometra lucunter, Echinometra viridis, Eucidaris tribuloides</t>
+  </si>
+  <si>
+    <t>• Each observed size class (fork length) of parrotfish in centimeters (cm) must be entered in Fork_length_cm; allowable values range from 0-9 to 50-59 cm in 10 cm increments</t>
+  </si>
+  <si>
+    <t>• Each observed size class (Test diameter ) of urchins in milimeters (mm) must be entered in Test_Diameter_mm; allowable values range from 0-20 to 80-100 mm in 20 mm increments</t>
+  </si>
+  <si>
+    <t>•  Count is the number of urchins of each species and size class observed within the survey area</t>
+  </si>
+  <si>
+    <t>Survey_Area_Parrotfish_m2</t>
+  </si>
+  <si>
+    <t>Survey_Area_Urchins_m2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Provide the area (in meters squared [m2]) where parrotfish surveys were conducted in Survey_Area_Parrotfish_m2; For example a 4 x 25 m belt transect would have a 100 m2 survey area </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Provide the area (in meters squared [m2]) where urchin surveys were conducted in Survey_Area_Urchins_m2; For example a 2 x 10 m belt transect would have a 20 m2 survey area </t>
+  </si>
+  <si>
+    <t>Sponges</t>
+  </si>
+  <si>
+    <t>• Allowable fields for Taxon include: Cliona aprica, Cliona caribbaea, Cliona tenuis, Cliona varians, Cliona delitrix, Siphonodictyon spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Sponges abundance should be quantified as total area in centimeters squared (cm2) occupied by each species; if survey data is instead in percent cover, it should be converted to area by multiplying the percent cover by Survey_Area_Sponges_m2 and then multiplying by 10,000 to covert m2 to cm2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Provide the area (in meters squared [m2]) where urchin surveys were conducted in Survey_Area_Sponges_m2; For example a 1 x 10 m belt transect would have a 10 m2 survey area </t>
+  </si>
+  <si>
+    <t>Survey_Area_Sponges_m2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +193,28 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -227,8 +237,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -247,9 +260,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Toth, Lauren T" id="{97EF6969-38CC-4F22-85CC-AA1DEB55A5EF}" userId="S::ltoth@usgs.gov::b1001b07-71f3-469e-89f6-892694f0967f" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -567,15 +578,117 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C1" dT="2026-06-22T15:50:51.57" personId="{97EF6969-38CC-4F22-85CC-AA1DEB55A5EF}" id="{E0961E5A-6428-4F0A-89BB-DD3400C64C05}">
-    <text>If blank will default to regional average</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B1F19CC-78B5-4ED5-B7BB-7FAE8CE47042}">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{097E6DCD-54F5-455D-97A6-7DF865AB568B}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -595,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -604,7 +717,7 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -624,8 +737,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E39944-BDAF-42EC-B85D-250380458002}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E39944-BDAF-42EC-B85D-250380458002}">
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -640,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -654,17 +767,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{20125FB6-2368-4231-BA26-450E353A76B7}">
       <formula1>"0-20, 20-40, 40-60, 60-80, 80-100"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{2223DC14-4EAE-4087-A2E5-F0D15F10AA0B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B1048576 B2" xr:uid="{2223DC14-4EAE-4087-A2E5-F0D15F10AA0B}">
       <formula1>"Diadema antillarum, Echinometra lucunter, Echinometra viridis, Eucidaris tribuloides"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14DD8175-6759-45E8-954F-11EB0116619A}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14DD8175-6759-45E8-954F-11EB0116619A}">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -679,24 +791,32 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{145A3965-54F2-4637-AAFD-B7BE6990F686}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B1048576 B2" xr:uid="{145A3965-54F2-4637-AAFD-B7BE6990F686}">
       <formula1>"Cliona aprica, Cliona caribbaea, Cliona tenuis, Cliona varians, Cliona delitrix, Siphonodictyon spp."</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca57789ecb406bb7a99068f68ac4c0ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89dc4794f4784a0bac47690674a3da53" ns2:_="" ns3:_="">
     <xsd:import namespace="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
@@ -891,15 +1011,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -912,6 +1023,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A206479D-07AC-477F-8545-4966E63B8E30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A81EFD0C-A7A2-40CC-AF34-FA5F0D62D046}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -930,14 +1049,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A206479D-07AC-477F-8545-4966E63B8E30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FB6342C-EC7C-49F8-97E7-6339AB75B937}">
   <ds:schemaRefs>
